--- a/sda_candidates.xlsx
+++ b/sda_candidates.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C01C31-7AB4-4B16-A3FC-266786FD9CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7115CD-81C6-482A-A2BB-6CD56CFDF2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>first name</t>
   </si>
@@ -59,9 +59,6 @@
     <t>layla.habib@example.com</t>
   </si>
   <si>
-    <t>6710c4e2f39ab5127c4d8e91</t>
-  </si>
-  <si>
     <t>Yousef</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>noura.alharbi@example.com</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Faisal</t>
   </si>
   <si>
@@ -90,13 +84,16 @@
   </si>
   <si>
     <t>FAISAL.RASHID@example.com</t>
+  </si>
+  <si>
+    <t>6ab0feb84e8ab2fb502820aa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +105,18 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -130,9 +139,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -509,11 +519,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>1022</v>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1003</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -523,11 +536,14 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
-        <v>1022</v>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1003</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -537,59 +553,66 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
-        <v>1022</v>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>1022</v>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1003</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="E6">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7">
-        <v>1022</v>
+      <c r="E7" s="2">
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/sda_candidates.xlsx
+++ b/sda_candidates.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7115CD-81C6-482A-A2BB-6CD56CFDF2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1292E9C9-7C05-441F-9803-8EE12A56B9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
     <t>FAISAL.RASHID@example.com</t>
   </si>
   <si>
-    <t>6ab0feb84e8ab2fb502820aa</t>
+    <t>6aafcfeac0f86295d8124f78</t>
   </si>
 </sst>
 </file>
